--- a/horario_semestre.xlsx
+++ b/horario_semestre.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="33">
   <si>
     <t>Lunes</t>
   </si>
@@ -33,6 +33,10 @@
   </si>
   <si>
     <t>9:00</t>
+  </si>
+  <si>
+    <t>Diseño de Software Verificable (B2)
+Reloj 102</t>
   </si>
   <si>
     <t>Introducción a la Programación (1)
@@ -46,7 +50,7 @@
   </si>
   <si>
     <t>Introducción a la Programación (2)
-Reloj 102</t>
+Reloj 103</t>
   </si>
   <si>
     <t>12:00</t>
@@ -62,7 +66,9 @@
   </si>
   <si>
     <t>Algoritmos y Complejidad (3)
-Ciencias 507</t>
+Reloj 104
+Computación Cuántica (A)
+Ciencias 505</t>
   </si>
   <si>
     <t>15:00</t>
@@ -98,10 +104,22 @@
     <t>Algoritmos y Complejidad (Sección 3)</t>
   </si>
   <si>
+    <t>Computación Cuántica (Sección A)</t>
+  </si>
+  <si>
+    <t>Diseño de Software Verificable (Sección B2)</t>
+  </si>
+  <si>
     <t>Reloj 102</t>
   </si>
   <si>
-    <t>Ciencias 507</t>
+    <t>Reloj 103</t>
+  </si>
+  <si>
+    <t>Reloj 104</t>
+  </si>
+  <si>
+    <t>Ciencias 505</t>
   </si>
 </sst>
 </file>
@@ -517,29 +535,31 @@
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -548,10 +568,10 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -560,10 +580,10 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -572,43 +592,43 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -626,75 +646,109 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
         <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
